--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -44,12 +44,12 @@
     <t>Description</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t>strike</t>
   </si>
   <si>
     <t>攻击</t>
@@ -92,9 +89,6 @@
     </r>
   </si>
   <si>
-    <t>strike+</t>
-  </si>
-  <si>
     <t>攻击+</t>
   </si>
   <si>
@@ -129,9 +123,6 @@
     </r>
   </si>
   <si>
-    <t>defend</t>
-  </si>
-  <si>
     <t>防御</t>
   </si>
   <si>
@@ -169,19 +160,10 @@
     </r>
   </si>
   <si>
-    <t>defend+</t>
-  </si>
-  <si>
     <t>防御+</t>
   </si>
   <si>
-    <t>heavy_blow</t>
-  </si>
-  <si>
     <t>猛击</t>
-  </si>
-  <si>
-    <t>heavy_blow+</t>
   </si>
   <si>
     <t>猛击+</t>
@@ -227,9 +209,6 @@
     </r>
   </si>
   <si>
-    <t>tactics</t>
-  </si>
-  <si>
     <t>战术</t>
   </si>
   <si>
@@ -264,9 +243,6 @@
     </r>
   </si>
   <si>
-    <t>tactics+</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -286,9 +262,6 @@
       </rPr>
       <t>+</t>
     </r>
-  </si>
-  <si>
-    <t>empower</t>
   </si>
   <si>
     <t>赋能</t>
@@ -322,9 +295,6 @@
       </rPr>
       <t>点能量。</t>
     </r>
-  </si>
-  <si>
-    <t>empower+</t>
   </si>
   <si>
     <r>
@@ -543,26 +513,26 @@
     </font>
     <font>
       <sz val="11.5"/>
-      <color theme="1"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
+      <color theme="1"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -1578,16 +1548,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1608,173 +1578,173 @@
       </c>
     </row>
     <row r="4" ht="15" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="1">
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="1">
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
+      <c r="A7" s="1">
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
+      <c r="A8" s="1">
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="16.2" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
+      <c r="A9" s="1">
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
+      <c r="A10" s="1">
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="16.2" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
+      <c r="A11" s="1">
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="16.2" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>34</v>
+      <c r="A12" s="1">
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="16.2" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>37</v>
+      <c r="A13" s="1">
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
-  <si>
-    <t>ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Key</t>
   </si>
   <si>
     <t>Name</t>
@@ -41,7 +44,10 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>Effects</t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
   <si>
     <t>int</t>
@@ -50,6 +56,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>资源标识</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -59,7 +68,10 @@
     <t>类型</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>图片</t>
   </si>
   <si>
     <t>攻击</t>
@@ -68,59 +80,16 @@
     <t>Attack</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
+    <t>[{"EffectId":1,"Value":6}]</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
   <si>
     <t>攻击+</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
+    <t>[{"EffectId":1,"Value":10}]</t>
   </si>
   <si>
     <t>防御</t>
@@ -129,118 +98,31 @@
     <t>Skill</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>获得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点格挡。</t>
-    </r>
+    <t>[{"EffectId":2,"Value":5}]</t>
   </si>
   <si>
     <t>防御+</t>
   </si>
   <si>
+    <t>[{"EffectId":1,"Value":8}]</t>
+  </si>
+  <si>
     <t>猛击</t>
   </si>
   <si>
+    <t>[{"EffectId":1,"Value":12}]</t>
+  </si>
+  <si>
     <t>猛击+</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
+    <t>[{"EffectId":1,"Value":16}]</t>
   </si>
   <si>
     <t>战术</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>抽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>张牌。</t>
-    </r>
+    <t>[{"EffectId":3,"Value":2}]</t>
   </si>
   <si>
     <r>
@@ -264,37 +146,13 @@
     </r>
   </si>
   <si>
+    <t>[{"EffectId":3,"Value":3}]</t>
+  </si>
+  <si>
     <t>赋能</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>获得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> {0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点能量。</t>
-    </r>
+    <t>[{"EffectId":4,"Value":1}]</t>
   </si>
   <si>
     <r>
@@ -318,35 +176,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>获得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点能量。</t>
-    </r>
+    <t>[{"EffectId":4,"Value":2}]</t>
   </si>
 </sst>
 </file>
@@ -359,7 +189,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,25 +340,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11.5"/>
@@ -1519,14 +1330,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="15.6666666666667" customWidth="1"/>
+    <col min="1" max="2" width="15.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="45.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1542,209 +1353,287 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:5">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:5">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:5">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:5">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:5">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="9" ht="16.2" spans="1:5">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="1:5">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="11" ht="16.2" spans="1:5">
+    <row r="11" ht="16.2" spans="1:7">
       <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="12" ht="16.2" spans="1:5">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="B12" s="1">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="13" ht="16.2" spans="1:5">
+    <row r="13" ht="16.2" spans="1:7">
       <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B13" s="1">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="1">
         <v>0</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Effects</t>
   </si>
   <si>
+    <t>NeedTarget</t>
+  </si>
+  <si>
     <t>Image</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>interesting</t>
+  </si>
+  <si>
     <t>资源标识</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t>效果</t>
+  </si>
+  <si>
+    <t>需要目标</t>
   </si>
   <si>
     <t>图片</t>
@@ -1330,14 +1339,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="15.6666666666667" customWidth="1"/>
     <col min="6" max="6" width="45.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1359,54 +1368,63 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1414,22 +1432,23 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -1437,22 +1456,23 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1460,22 +1480,23 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1483,22 +1504,23 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1506,22 +1528,23 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1529,22 +1552,23 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1552,22 +1576,23 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="11" ht="16.2" spans="1:7">
+    <row r="11" ht="16.2" spans="1:8">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1575,22 +1600,23 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1598,22 +1624,23 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="13" ht="16.2" spans="1:7">
+    <row r="13" ht="16.2" spans="1:8">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1621,19 +1648,20 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF91A0E-6C61-43DA-90A9-2E9E77E4F83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF670451-0786-416A-B136-5CD85CD588A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
   <si>
     <t>Id</t>
   </si>
@@ -191,6 +191,18 @@
   </si>
   <si>
     <t>Effects</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚弱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":5,"Value":1}]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -736,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -1051,6 +1063,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF670451-0786-416A-B136-5CD85CD588A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97CC9E9-6E4A-4A98-BDFF-400ECDF572C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>防御+</t>
   </si>
   <si>
-    <t>[{"EffectId":1,"Value":8}]</t>
-  </si>
-  <si>
     <t>猛击</t>
   </si>
   <si>
@@ -203,6 +200,10 @@
   </si>
   <si>
     <t>[{"EffectId":5,"Value":1}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":8}]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -772,7 +773,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -850,7 +851,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -918,8 +919,8 @@
       <c r="E7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" t="s">
-        <v>26</v>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -933,7 +934,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -942,7 +943,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -956,7 +957,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -965,7 +966,7 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -979,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -988,7 +989,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -1002,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1011,7 +1012,7 @@
         <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -1025,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1034,7 +1035,7 @@
         <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -1048,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1057,7 +1058,7 @@
         <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -1071,16 +1072,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97CC9E9-6E4A-4A98-BDFF-400ECDF572C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96BE03A-3BA5-42DB-8AF9-3482BF0294D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>Id</t>
   </si>
@@ -51,9 +51,6 @@
     <t>NeedTarget</t>
   </si>
   <si>
-    <t>Image</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -82,9 +79,6 @@
   </si>
   <si>
     <t>图片</t>
-  </si>
-  <si>
-    <t>攻击</t>
   </si>
   <si>
     <t>Attack</t>
@@ -204,6 +198,20 @@
   </si>
   <si>
     <t>[{"EffectId":2,"Value":8}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>打击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>strike_ironclad</t>
+  </si>
+  <si>
+    <t>defend_ironclad</t>
+  </si>
+  <si>
+    <t>IconName</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -773,39 +781,39 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -813,25 +821,25 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -841,20 +849,20 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
+      <c r="C4" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -865,19 +873,19 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -888,19 +896,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -911,19 +919,19 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -934,19 +942,19 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -957,19 +965,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -980,19 +988,19 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.25">
@@ -1003,19 +1011,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1026,19 +1034,19 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" x14ac:dyDescent="0.25">
@@ -1049,19 +1057,19 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1072,19 +1080,19 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96BE03A-3BA5-42DB-8AF9-3482BF0294D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78101386-68B0-4237-B4A4-29ADA295B8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>Id</t>
   </si>
@@ -103,18 +103,6 @@
   </si>
   <si>
     <t>防御+</t>
-  </si>
-  <si>
-    <t>猛击</t>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":12}]</t>
-  </si>
-  <si>
-    <t>猛击+</t>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":16}]</t>
   </si>
   <si>
     <t>战术</t>
@@ -213,6 +201,25 @@
   <si>
     <t>IconName</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛击+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":1}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":1}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bash</t>
   </si>
 </sst>
 </file>
@@ -781,13 +788,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -850,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -859,10 +866,10 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -885,7 +892,7 @@
         <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -908,7 +915,7 @@
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -928,10 +935,10 @@
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -941,8 +948,8 @@
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -950,11 +957,11 @@
       <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
-        <v>25</v>
+      <c r="F8" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -964,8 +971,8 @@
       <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
-        <v>26</v>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -973,11 +980,11 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="F9" t="s">
-        <v>27</v>
+      <c r="F9" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -988,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -997,7 +1004,7 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -1011,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1020,7 +1027,7 @@
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1034,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1043,7 +1050,7 @@
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1057,7 +1064,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1066,7 +1073,7 @@
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1080,16 +1087,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1098,5 +1105,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78101386-68B0-4237-B4A4-29ADA295B8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB220C5-0166-485E-B840-167F722F6833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>攻击+</t>
   </si>
   <si>
-    <t>[{"EffectId":1,"Value":10}]</t>
-  </si>
-  <si>
     <t>防御</t>
   </si>
   <si>
@@ -211,15 +208,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":1}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":1}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>bash</t>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":9}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":3}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -788,13 +789,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -857,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -866,10 +867,10 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -888,11 +889,11 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>19</v>
+      <c r="F5" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,19 +904,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -926,19 +927,19 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -949,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -958,10 +959,10 @@
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -972,7 +973,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -981,10 +982,10 @@
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -995,16 +996,16 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -1018,16 +1019,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1041,16 +1042,16 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1064,16 +1065,16 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1087,16 +1088,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB220C5-0166-485E-B840-167F722F6833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D90C42-C472-414A-97BE-A66B9217B505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -48,18 +48,12 @@
     <t>Type</t>
   </si>
   <si>
-    <t>NeedTarget</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>interesting</t>
-  </si>
-  <si>
     <t>资源标识</t>
   </si>
   <si>
@@ -73,9 +67,6 @@
   </si>
   <si>
     <t>效果</t>
-  </si>
-  <si>
-    <t>需要目标</t>
   </si>
   <si>
     <t>图片</t>
@@ -170,18 +161,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>虚弱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":5,"Value":1}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"EffectId":2,"Value":8}]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -220,6 +199,22 @@
   </si>
   <si>
     <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardEffectEntry[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -765,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -789,39 +784,39 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
+      <c r="F2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -829,25 +824,25 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -858,19 +853,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -881,19 +879,22 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -904,19 +905,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -927,19 +931,22 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -950,19 +957,22 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -973,19 +983,22 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -996,19 +1009,22 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.25">
@@ -1019,19 +1035,22 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1042,19 +1061,22 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" x14ac:dyDescent="0.25">
@@ -1065,42 +1087,22 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D90C42-C472-414A-97BE-A66B9217B505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B806EEB-93EB-498D-B692-4A04AA2CE5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,14 +31,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>Key</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>资源标识</t>
   </si>
   <si>
     <t>名称</t>
@@ -175,10 +169,6 @@
     <t>defend_ironclad</t>
   </si>
   <si>
-    <t>IconName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>痛击</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -215,6 +205,10 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -760,349 +754,310 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="64.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="s">
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5">
-        <v>2</v>
+      <c r="B5" t="s">
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6">
-        <v>3</v>
+      <c r="B6" t="s">
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>4</v>
+      <c r="B7" t="s">
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>5</v>
+      <c r="B8" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>6</v>
       </c>
-      <c r="H8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9">
-        <v>6</v>
+      <c r="B9" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>7</v>
+      <c r="B10" t="s">
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10">
         <v>8</v>
       </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11">
-        <v>8</v>
+      <c r="B11" t="s">
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12">
-        <v>9</v>
+      <c r="B12" t="s">
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13">
-        <v>10</v>
+      <c r="B13" t="s">
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13">
         <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B806EEB-93EB-498D-B692-4A04AA2CE5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C9480B-04C6-4B83-86EA-FB2F8CCD8442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -66,101 +66,32 @@
     <t>图片</t>
   </si>
   <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>攻击+</t>
   </si>
   <si>
     <t>防御</t>
   </si>
   <si>
-    <t>Skill</t>
-  </si>
-  <si>
     <t>[{"EffectId":2,"Value":5}]</t>
   </si>
   <si>
     <t>防御+</t>
   </si>
   <si>
-    <t>战术</t>
-  </si>
-  <si>
-    <t>[{"EffectId":3,"Value":2}]</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>战术</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>+</t>
-    </r>
-  </si>
-  <si>
-    <t>[{"EffectId":3,"Value":3}]</t>
-  </si>
-  <si>
-    <t>赋能</t>
-  </si>
-  <si>
-    <t>[{"EffectId":4,"Value":1}]</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>赋能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>+</t>
-    </r>
-  </si>
-  <si>
-    <t>[{"EffectId":4,"Value":2}]</t>
-  </si>
-  <si>
     <t>[{"EffectId":1,"Value":6}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Effects</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"EffectId":2,"Value":8}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>打击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>strike_ironclad</t>
@@ -170,65 +101,93 @@
   </si>
   <si>
     <t>痛击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>痛击+</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>bash</t>
   </si>
   <si>
     <t>[{"EffectId":1,"Value":9}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":3}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UpgradeId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>强化id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CardEffectEntry[]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>愤怒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>愤怒+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑柄打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑柄打击+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anger</t>
+  </si>
+  <si>
+    <t>anger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pommel_strike</t>
+  </si>
+  <si>
+    <t>attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -271,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -766,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -778,10 +737,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -801,10 +760,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -827,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -835,19 +794,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -858,19 +817,19 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>11</v>
+      <c r="E5" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -881,19 +840,19 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>15</v>
+      <c r="E6" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -904,19 +863,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>15</v>
+      <c r="E7" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -927,19 +886,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="E8" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -950,19 +909,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -972,43 +931,37 @@
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1019,49 +972,43 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C9480B-04C6-4B83-86EA-FB2F8CCD8442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846B8749-05D5-4EC1-912C-554B4862E160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,6 +192,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846B8749-05D5-4EC1-912C-554B4862E160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718BA9DA-D8BB-4CFF-B402-BB068FDA0E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -75,105 +75,153 @@
     <t>[{"EffectId":2,"Value":5}]</t>
   </si>
   <si>
+    <t>[{"EffectId":1,"Value":6}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":8}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strike_ironclad</t>
+  </si>
+  <si>
+    <t>defend_ironclad</t>
+  </si>
+  <si>
+    <t>痛击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>痛击+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":9}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":3}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardEffectEntry[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑柄打击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑柄打击+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":9},{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":1,"Value":10},{"EffectId":3,"Value":2}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pommel_strike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrug_it_off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耸肩无视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":8},{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":11},{"EffectId":3,"Value":1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blood_wall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":6,"Value":2},{"EffectId":2,"Value":16}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":6,"Value":2},{"EffectId":2,"Value":20}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_wave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defend_ironclad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>防御+</t>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":6}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":2,"Value":8}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>strike_ironclad</t>
-  </si>
-  <si>
-    <t>defend_ironclad</t>
-  </si>
-  <si>
-    <t>痛击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>痛击+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bash</t>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":9}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":10},{"EffectId":5,"Value":3}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"EffectId":1,"Value":8},{"EffectId":5,"Value":2}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强化id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardEffectEntry[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>愤怒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>愤怒+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑柄打击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑柄打击+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>anger</t>
-  </si>
-  <si>
-    <t>anger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pommel_strike</t>
-  </si>
-  <si>
-    <t>attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁斩波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":5},{"EffectId":1,"Value":5}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"EffectId":2,"Value":7},{"EffectId":1,"Value":7}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -714,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -726,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -738,10 +786,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -761,10 +809,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -787,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -795,19 +843,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -818,7 +866,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -827,10 +875,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -841,7 +889,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -850,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -860,128 +908,137 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7">
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
+      <c r="B8" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>39</v>
+      <c r="F10" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="G10">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>39</v>
       </c>
       <c r="G12">
@@ -989,24 +1046,159 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
